--- a/cmd/groups/specimen.xlsx
+++ b/cmd/groups/specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\go\src\github.com\tranners\fyne-xlsx\cmd\groups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8657AB-1526-45A1-AC5E-1CB9909A493E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644D35B0-3DF6-46F6-A37E-366B69C8DF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="26460" windowHeight="16170" xr2:uid="{18453F22-C442-461A-B1D5-BC6CD41F0A82}"/>
+    <workbookView xWindow="1950" yWindow="2520" windowWidth="24735" windowHeight="13230" xr2:uid="{18453F22-C442-461A-B1D5-BC6CD41F0A82}"/>
   </bookViews>
   <sheets>
     <sheet name="No Freeze Pane" sheetId="18" r:id="rId1"/>
@@ -1306,6 +1306,15 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1386,15 +1395,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
@@ -1722,18 +1722,16 @@
   <dimension ref="A1:AT31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="5.5703125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5703125" customWidth="1"/>
-    <col min="5" max="7" width="5.5703125" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="9" width="5.5703125" customWidth="1"/>
+    <col min="1" max="4" width="5" hidden="1" customWidth="1"/>
+    <col min="5" max="7" width="5.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="5.5703125" hidden="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="5.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="11" width="9.7109375" customWidth="1"/>
     <col min="12" max="12" width="6.42578125" customWidth="1"/>
     <col min="13" max="13" width="14.5703125" customWidth="1"/>
     <col min="14" max="14" width="23.85546875" customWidth="1"/>
-    <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="6.42578125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="10" hidden="1" customWidth="1"/>
+    <col min="15" max="18" width="4.5703125" customWidth="1"/>
     <col min="19" max="19" width="9.140625" customWidth="1" outlineLevel="6"/>
     <col min="20" max="20" width="8.42578125" customWidth="1" outlineLevel="6"/>
     <col min="21" max="21" width="9.28515625" customWidth="1" outlineLevel="5"/>
@@ -1754,7 +1752,7 @@
     <col min="39" max="39" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20">
         <v>1</v>
       </c>
@@ -1921,7 +1919,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:46" ht="18.75" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" ht="12.75" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>22</v>
       </c>
@@ -2087,7 +2085,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:46" ht="16.5" customHeight="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:46" ht="12.75" hidden="1" customHeight="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>27</v>
       </c>
@@ -2253,7 +2251,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="16.5" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46" ht="12.75" hidden="1" customHeight="1" outlineLevel="1" collapsed="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>27</v>
       </c>
@@ -2321,11 +2319,11 @@
         <f t="shared" si="3"/>
         <v>84</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="W4" s="99"/>
-      <c r="X4" s="100"/>
+      <c r="W4" s="102"/>
+      <c r="X4" s="103"/>
       <c r="Y4" s="50">
         <f t="shared" si="2"/>
         <v>100</v>
@@ -2410,7 +2408,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46" ht="12.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>27</v>
       </c>
@@ -2474,9 +2472,9 @@
         <f t="shared" si="3"/>
         <v>105</v>
       </c>
-      <c r="V5" s="101"/>
-      <c r="W5" s="102"/>
-      <c r="X5" s="103"/>
+      <c r="V5" s="104"/>
+      <c r="W5" s="105"/>
+      <c r="X5" s="106"/>
       <c r="Y5" s="13">
         <v>62</v>
       </c>
@@ -2564,7 +2562,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:46" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46" ht="12.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -2626,9 +2624,9 @@
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
-      <c r="V6" s="101"/>
-      <c r="W6" s="102"/>
-      <c r="X6" s="103"/>
+      <c r="V6" s="104"/>
+      <c r="W6" s="105"/>
+      <c r="X6" s="106"/>
       <c r="Y6" s="13">
         <v>0</v>
       </c>
@@ -2716,7 +2714,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:46" ht="15.75" customHeight="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:46" ht="13.5" customHeight="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>44</v>
       </c>
@@ -2778,9 +2776,9 @@
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-      <c r="V7" s="104"/>
-      <c r="W7" s="105"/>
-      <c r="X7" s="106"/>
+      <c r="V7" s="107"/>
+      <c r="W7" s="108"/>
+      <c r="X7" s="109"/>
       <c r="Y7">
         <v>5</v>
       </c>
@@ -2929,8 +2927,8 @@
         <v>168</v>
       </c>
       <c r="V8">
-        <f t="shared" si="0"/>
-        <v>176</v>
+        <f>COLUMN()</f>
+        <v>22</v>
       </c>
       <c r="W8">
         <f t="shared" si="0"/>
@@ -3441,13 +3439,13 @@
         <f t="shared" si="1"/>
         <v>308</v>
       </c>
-      <c r="AC11" s="107" t="s">
+      <c r="AC11" s="110" t="s">
         <v>34</v>
       </c>
-      <c r="AD11" s="107"/>
-      <c r="AE11" s="107"/>
-      <c r="AF11" s="107"/>
-      <c r="AG11" s="107"/>
+      <c r="AD11" s="110"/>
+      <c r="AE11" s="110"/>
+      <c r="AF11" s="110"/>
+      <c r="AG11" s="110"/>
       <c r="AH11">
         <f t="shared" si="1"/>
         <v>374</v>
@@ -3587,11 +3585,11 @@
         <f t="shared" si="1"/>
         <v>336</v>
       </c>
-      <c r="AC12" s="107"/>
-      <c r="AD12" s="107"/>
-      <c r="AE12" s="107"/>
-      <c r="AF12" s="107"/>
-      <c r="AG12" s="107"/>
+      <c r="AC12" s="110"/>
+      <c r="AD12" s="110"/>
+      <c r="AE12" s="110"/>
+      <c r="AF12" s="110"/>
+      <c r="AG12" s="110"/>
       <c r="AH12">
         <f t="shared" si="1"/>
         <v>408</v>
@@ -3736,11 +3734,11 @@
         <f t="shared" si="1"/>
         <v>364</v>
       </c>
-      <c r="AC13" s="107"/>
-      <c r="AD13" s="107"/>
-      <c r="AE13" s="107"/>
-      <c r="AF13" s="107"/>
-      <c r="AG13" s="107"/>
+      <c r="AC13" s="110"/>
+      <c r="AD13" s="110"/>
+      <c r="AE13" s="110"/>
+      <c r="AF13" s="110"/>
+      <c r="AG13" s="110"/>
       <c r="AH13">
         <f t="shared" si="1"/>
         <v>442</v>
@@ -3885,11 +3883,11 @@
         <f t="shared" si="2"/>
         <v>392</v>
       </c>
-      <c r="AC14" s="107"/>
-      <c r="AD14" s="107"/>
-      <c r="AE14" s="107"/>
-      <c r="AF14" s="107"/>
-      <c r="AG14" s="107"/>
+      <c r="AC14" s="110"/>
+      <c r="AD14" s="110"/>
+      <c r="AE14" s="110"/>
+      <c r="AF14" s="110"/>
+      <c r="AG14" s="110"/>
       <c r="AH14">
         <f t="shared" si="2"/>
         <v>476</v>
@@ -4139,22 +4137,22 @@
       <c r="J16" s="1">
         <v>32</v>
       </c>
-      <c r="K16" s="108" t="s">
+      <c r="K16" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="L16" s="109"/>
-      <c r="M16" s="109"/>
-      <c r="N16" s="109"/>
-      <c r="O16" s="109"/>
-      <c r="P16" s="109"/>
-      <c r="Q16" s="109"/>
-      <c r="R16" s="109"/>
-      <c r="S16" s="109"/>
-      <c r="T16" s="109"/>
-      <c r="U16" s="109"/>
-      <c r="V16" s="109"/>
-      <c r="W16" s="109"/>
-      <c r="X16" s="110"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="81"/>
+      <c r="O16" s="81"/>
+      <c r="P16" s="81"/>
+      <c r="Q16" s="81"/>
+      <c r="R16" s="81"/>
+      <c r="S16" s="81"/>
+      <c r="T16" s="81"/>
+      <c r="U16" s="81"/>
+      <c r="V16" s="81"/>
+      <c r="W16" s="81"/>
+      <c r="X16" s="82"/>
       <c r="Y16">
         <f t="shared" si="2"/>
         <v>400</v>
@@ -4363,7 +4361,7 @@
         <f t="shared" si="2"/>
         <v>595</v>
       </c>
-      <c r="AJ17" s="97">
+      <c r="AJ17" s="100">
         <f t="shared" si="4"/>
         <v>612</v>
       </c>
@@ -4526,7 +4524,7 @@
         <f t="shared" si="2"/>
         <v>630</v>
       </c>
-      <c r="AJ18" s="97"/>
+      <c r="AJ18" s="100"/>
       <c r="AK18">
         <f t="shared" si="4"/>
         <v>666</v>
@@ -4686,7 +4684,7 @@
         <f t="shared" si="2"/>
         <v>665</v>
       </c>
-      <c r="AJ19" s="97"/>
+      <c r="AJ19" s="100"/>
       <c r="AK19">
         <f t="shared" si="4"/>
         <v>703</v>
@@ -4846,7 +4844,7 @@
         <f t="shared" si="2"/>
         <v>700</v>
       </c>
-      <c r="AJ20" s="97"/>
+      <c r="AJ20" s="100"/>
       <c r="AK20">
         <f t="shared" si="4"/>
         <v>740</v>
@@ -5007,7 +5005,7 @@
         <f t="shared" si="2"/>
         <v>735</v>
       </c>
-      <c r="AJ21" s="97"/>
+      <c r="AJ21" s="100"/>
       <c r="AK21">
         <f t="shared" si="4"/>
         <v>777</v>
@@ -5080,12 +5078,12 @@
       <c r="J22">
         <v>44</v>
       </c>
-      <c r="K22" s="80" t="s">
+      <c r="K22" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="L22" s="81"/>
-      <c r="M22" s="81"/>
-      <c r="N22" s="82"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="85"/>
       <c r="O22">
         <v>132</v>
       </c>
@@ -5098,14 +5096,14 @@
       <c r="R22">
         <v>198</v>
       </c>
-      <c r="S22" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="T22" s="90"/>
-      <c r="U22" s="91"/>
-      <c r="V22" s="90"/>
-      <c r="W22" s="91"/>
-      <c r="X22" s="92"/>
+      <c r="S22" s="92" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="93"/>
+      <c r="U22" s="94"/>
+      <c r="V22" s="93"/>
+      <c r="W22" s="94"/>
+      <c r="X22" s="95"/>
       <c r="Y22">
         <f t="shared" si="2"/>
         <v>550</v>
@@ -5150,7 +5148,7 @@
         <f t="shared" si="2"/>
         <v>770</v>
       </c>
-      <c r="AJ22" s="97"/>
+      <c r="AJ22" s="100"/>
       <c r="AK22">
         <f t="shared" si="4"/>
         <v>814</v>
@@ -5225,10 +5223,10 @@
         <f t="shared" si="6"/>
         <v>230</v>
       </c>
-      <c r="K23" s="83"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="84"/>
-      <c r="N23" s="85"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="87"/>
+      <c r="M23" s="87"/>
+      <c r="N23" s="88"/>
       <c r="O23">
         <f t="shared" si="6"/>
         <v>345</v>
@@ -5245,12 +5243,12 @@
         <f t="shared" si="6"/>
         <v>414</v>
       </c>
-      <c r="S23" s="93"/>
-      <c r="T23" s="90"/>
-      <c r="U23" s="90"/>
-      <c r="V23" s="90"/>
-      <c r="W23" s="90"/>
-      <c r="X23" s="92"/>
+      <c r="S23" s="96"/>
+      <c r="T23" s="93"/>
+      <c r="U23" s="93"/>
+      <c r="V23" s="93"/>
+      <c r="W23" s="93"/>
+      <c r="X23" s="95"/>
       <c r="Y23">
         <f t="shared" si="2"/>
         <v>575</v>
@@ -5295,7 +5293,7 @@
         <f t="shared" si="2"/>
         <v>805</v>
       </c>
-      <c r="AJ23" s="97"/>
+      <c r="AJ23" s="100"/>
       <c r="AK23">
         <f t="shared" si="4"/>
         <v>851</v>
@@ -5370,10 +5368,10 @@
         <f t="shared" si="6"/>
         <v>240</v>
       </c>
-      <c r="K24" s="86"/>
-      <c r="L24" s="87"/>
-      <c r="M24" s="87"/>
-      <c r="N24" s="88"/>
+      <c r="K24" s="89"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="91"/>
       <c r="O24">
         <f t="shared" si="6"/>
         <v>360</v>
@@ -5390,12 +5388,12 @@
         <f t="shared" si="6"/>
         <v>432</v>
       </c>
-      <c r="S24" s="94"/>
-      <c r="T24" s="90"/>
-      <c r="U24" s="95"/>
-      <c r="V24" s="90"/>
-      <c r="W24" s="95"/>
-      <c r="X24" s="96"/>
+      <c r="S24" s="97"/>
+      <c r="T24" s="93"/>
+      <c r="U24" s="98"/>
+      <c r="V24" s="93"/>
+      <c r="W24" s="98"/>
+      <c r="X24" s="99"/>
       <c r="Y24">
         <f t="shared" si="2"/>
         <v>600</v>
@@ -5440,7 +5438,7 @@
         <f t="shared" si="2"/>
         <v>840</v>
       </c>
-      <c r="AJ24" s="97"/>
+      <c r="AJ24" s="100"/>
       <c r="AK24">
         <f t="shared" si="4"/>
         <v>888</v>
@@ -5611,7 +5609,7 @@
         <f t="shared" si="2"/>
         <v>875</v>
       </c>
-      <c r="AJ25" s="97"/>
+      <c r="AJ25" s="100"/>
       <c r="AK25">
         <f t="shared" si="4"/>
         <v>925</v>
@@ -5782,7 +5780,7 @@
         <f t="shared" si="2"/>
         <v>910</v>
       </c>
-      <c r="AJ26" s="97"/>
+      <c r="AJ26" s="100"/>
       <c r="AK26">
         <f t="shared" si="4"/>
         <v>962</v>
@@ -5953,7 +5951,7 @@
         <f t="shared" si="2"/>
         <v>945</v>
       </c>
-      <c r="AJ27" s="97"/>
+      <c r="AJ27" s="100"/>
       <c r="AK27">
         <f t="shared" si="4"/>
         <v>999</v>
@@ -6124,7 +6122,7 @@
         <f t="shared" si="2"/>
         <v>980</v>
       </c>
-      <c r="AJ28" s="97"/>
+      <c r="AJ28" s="100"/>
       <c r="AK28">
         <f t="shared" si="4"/>
         <v>1036</v>

--- a/cmd/groups/specimen.xlsx
+++ b/cmd/groups/specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\go\src\github.com\tranners\fyne-xlsx\cmd\groups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644D35B0-3DF6-46F6-A37E-366B69C8DF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FC7098-1490-4427-BD93-2D8E712053AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="2520" windowWidth="24735" windowHeight="13230" xr2:uid="{18453F22-C442-461A-B1D5-BC6CD41F0A82}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22965" windowHeight="17985" xr2:uid="{18453F22-C442-461A-B1D5-BC6CD41F0A82}"/>
   </bookViews>
   <sheets>
     <sheet name="No Freeze Pane" sheetId="18" r:id="rId1"/>
@@ -1722,10 +1722,9 @@
   <dimension ref="A1:AT31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="5" hidden="1" customWidth="1"/>
-    <col min="5" max="7" width="5.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="5.5703125" hidden="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="5.5703125" customWidth="1"/>
+    <col min="1" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="7" width="4.7109375" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="11" width="9.7109375" customWidth="1"/>
     <col min="12" max="12" width="6.42578125" customWidth="1"/>
@@ -1752,7 +1751,7 @@
     <col min="39" max="39" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20">
         <v>1</v>
       </c>
@@ -1919,7 +1918,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:46" ht="12.75" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" ht="12.75" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>22</v>
       </c>
@@ -2085,7 +2084,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:46" ht="12.75" hidden="1" customHeight="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:46" ht="12.75" customHeight="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>27</v>
       </c>
@@ -2251,7 +2250,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="12.75" hidden="1" customHeight="1" outlineLevel="1" collapsed="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46" ht="12.75" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>27</v>
       </c>
@@ -2408,7 +2407,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="12.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46" ht="12.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>27</v>
       </c>
@@ -2562,7 +2561,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:46" ht="12.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46" ht="12.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -2714,7 +2713,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:46" ht="13.5" customHeight="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:46" ht="12.75" customHeight="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>44</v>
       </c>

--- a/cmd/groups/specimen.xlsx
+++ b/cmd/groups/specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\go\src\github.com\tranners\fyne-xlsx\cmd\groups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FC7098-1490-4427-BD93-2D8E712053AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62FECDD-F9E9-4B10-99D2-51F0A15FDF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="22965" windowHeight="17985" xr2:uid="{18453F22-C442-461A-B1D5-BC6CD41F0A82}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="12345" xr2:uid="{18453F22-C442-461A-B1D5-BC6CD41F0A82}"/>
   </bookViews>
   <sheets>
     <sheet name="No Freeze Pane" sheetId="18" r:id="rId1"/>
@@ -86,9 +86,6 @@
     <t>4.Hello</t>
   </si>
   <si>
-    <t>6. Hello World, Hello World; Hello</t>
-  </si>
-  <si>
     <t>7. Hello World, Hello World</t>
   </si>
   <si>
@@ -108,9 +105,6 @@
   </si>
   <si>
     <t>Unclipped; Centred</t>
-  </si>
-  <si>
-    <t>5. Hello World, Hello Worldss</t>
   </si>
   <si>
     <t>9. Hello. He Was Clipped, Again</t>
@@ -141,6 +135,12 @@
   </si>
   <si>
     <t>XYX</t>
+  </si>
+  <si>
+    <t>6. Hello World,</t>
+  </si>
+  <si>
+    <t>5. Hello World</t>
   </si>
 </sst>
 </file>
@@ -233,7 +233,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -299,12 +299,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5FFF0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="75">
     <border>
@@ -485,32 +479,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
@@ -1166,12 +1134,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1211,16 +1201,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1254,20 +1242,26 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="45" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1277,12 +1271,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
@@ -1290,87 +1280,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1379,22 +1340,53 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
@@ -1732,10 +1724,10 @@
     <col min="14" max="14" width="23.85546875" customWidth="1"/>
     <col min="15" max="18" width="4.5703125" customWidth="1"/>
     <col min="19" max="19" width="9.140625" customWidth="1" outlineLevel="6"/>
-    <col min="20" max="20" width="8.42578125" customWidth="1" outlineLevel="6"/>
+    <col min="20" max="20" width="0.5703125" customWidth="1" outlineLevel="6"/>
     <col min="21" max="21" width="9.28515625" customWidth="1" outlineLevel="5"/>
     <col min="22" max="22" width="9.140625" customWidth="1" outlineLevel="4"/>
-    <col min="23" max="23" width="5.7109375" customWidth="1" outlineLevel="3"/>
+    <col min="23" max="23" width="0.5703125" customWidth="1" outlineLevel="3"/>
     <col min="24" max="24" width="9.140625" customWidth="1" outlineLevel="2"/>
     <col min="25" max="25" width="7" customWidth="1" outlineLevel="1"/>
     <col min="27" max="27" width="9.140625" customWidth="1"/>
@@ -1792,7 +1784,7 @@
         <v>2</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O1" s="21">
         <v>5</v>
@@ -1829,11 +1821,11 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="Y1" s="50">
+      <c r="Y1" s="48">
         <f>ROW()*COLUMN()</f>
         <v>25</v>
       </c>
-      <c r="Z1" s="51">
+      <c r="Z1" s="49">
         <f t="shared" ref="Z1:AT13" si="1">ROW()*COLUMN()</f>
         <v>26</v>
       </c>
@@ -1949,20 +1941,20 @@
       <c r="J2" s="20">
         <v>2</v>
       </c>
-      <c r="K2" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="36">
+      <c r="K2" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="34">
         <v>2</v>
       </c>
-      <c r="M2" s="36">
+      <c r="M2" s="34">
         <v>2</v>
       </c>
-      <c r="N2" s="74" t="s">
+      <c r="N2" s="72" t="s">
         <v>6</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P2">
         <v>9</v>
@@ -1996,11 +1988,11 @@
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="Y2" s="50">
+      <c r="Y2" s="48">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="Z2" s="51">
+      <c r="Z2" s="49">
         <v>6</v>
       </c>
       <c r="AA2">
@@ -2085,8 +2077,8 @@
       </c>
     </row>
     <row r="3" spans="1:46" ht="12.75" customHeight="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
-        <v>27</v>
+      <c r="A3" s="29" t="s">
+        <v>25</v>
       </c>
       <c r="B3" s="20">
         <v>1</v>
@@ -2115,20 +2107,20 @@
       <c r="J3">
         <v>2</v>
       </c>
-      <c r="K3" s="37" t="s">
+      <c r="K3" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="34">
+      <c r="L3" s="32">
         <v>2</v>
       </c>
-      <c r="M3" s="34">
+      <c r="M3" s="32">
         <v>2</v>
       </c>
-      <c r="N3" s="75" t="s">
+      <c r="N3" s="73" t="s">
         <v>5</v>
       </c>
       <c r="O3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P3" s="21">
         <v>21</v>
@@ -2162,11 +2154,11 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="Y3" s="50">
+      <c r="Y3" s="48">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="Z3" s="51">
+      <c r="Z3" s="49">
         <v>5</v>
       </c>
       <c r="AA3">
@@ -2252,7 +2244,7 @@
     </row>
     <row r="4" spans="1:46" ht="12.75" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" s="20">
         <v>1</v>
@@ -2281,20 +2273,20 @@
       <c r="J4">
         <v>2</v>
       </c>
-      <c r="K4" s="38" t="s">
+      <c r="K4" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="32">
         <v>2</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="32">
         <v>2</v>
       </c>
-      <c r="N4" s="75" t="s">
+      <c r="N4" s="73" t="s">
         <v>4</v>
       </c>
       <c r="O4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P4">
         <v>28</v>
@@ -2318,16 +2310,16 @@
         <f t="shared" si="3"/>
         <v>84</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="W4" s="102"/>
-      <c r="X4" s="103"/>
-      <c r="Y4" s="50">
+      <c r="W4" s="88"/>
+      <c r="X4" s="89"/>
+      <c r="Y4" s="48">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="Z4" s="51">
+      <c r="Z4" s="49">
         <v>5</v>
       </c>
       <c r="AB4">
@@ -2409,7 +2401,7 @@
     </row>
     <row r="5" spans="1:46" ht="12.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="20">
         <v>1</v>
@@ -2438,18 +2430,18 @@
       <c r="J5">
         <v>2</v>
       </c>
-      <c r="K5" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="34">
+      <c r="K5" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="37"/>
+      <c r="M5" s="32">
         <v>2</v>
       </c>
-      <c r="N5" s="75" t="s">
+      <c r="N5" s="73" t="s">
         <v>7</v>
       </c>
       <c r="O5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P5">
         <v>35</v>
@@ -2471,9 +2463,9 @@
         <f t="shared" si="3"/>
         <v>105</v>
       </c>
-      <c r="V5" s="104"/>
-      <c r="W5" s="105"/>
-      <c r="X5" s="106"/>
+      <c r="V5" s="90"/>
+      <c r="W5" s="91"/>
+      <c r="X5" s="92"/>
       <c r="Y5" s="13">
         <v>62</v>
       </c>
@@ -2592,16 +2584,16 @@
       <c r="J6">
         <v>12</v>
       </c>
-      <c r="K6" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="75" t="s">
+      <c r="K6" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="73" t="s">
         <v>8</v>
       </c>
       <c r="O6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P6">
         <v>42</v>
@@ -2623,9 +2615,9 @@
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
-      <c r="V6" s="104"/>
-      <c r="W6" s="105"/>
-      <c r="X6" s="106"/>
+      <c r="V6" s="90"/>
+      <c r="W6" s="91"/>
+      <c r="X6" s="92"/>
       <c r="Y6" s="13">
         <v>0</v>
       </c>
@@ -2742,18 +2734,18 @@
         <v>1</v>
       </c>
       <c r="J7" s="23"/>
-      <c r="K7" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="41">
+      <c r="K7" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="39">
         <v>33</v>
       </c>
-      <c r="M7" s="41"/>
-      <c r="N7" s="75" t="s">
+      <c r="M7" s="39"/>
+      <c r="N7" s="73" t="s">
         <v>9</v>
       </c>
       <c r="O7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P7">
         <v>49</v>
@@ -2761,13 +2753,13 @@
       <c r="Q7">
         <v>56</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="76">
         <v>5</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="76">
         <v>70</v>
       </c>
-      <c r="T7" s="78">
+      <c r="T7" s="76">
         <f t="shared" si="2"/>
         <v>140</v>
       </c>
@@ -2775,9 +2767,9 @@
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-      <c r="V7" s="107"/>
-      <c r="W7" s="108"/>
-      <c r="X7" s="109"/>
+      <c r="V7" s="93"/>
+      <c r="W7" s="94"/>
+      <c r="X7" s="95"/>
       <c r="Y7">
         <v>5</v>
       </c>
@@ -2892,18 +2884,18 @@
         <v>1</v>
       </c>
       <c r="J8" s="23"/>
-      <c r="K8" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="34">
+      <c r="K8" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" s="32">
         <v>8</v>
       </c>
-      <c r="M8" s="34"/>
-      <c r="N8" s="75" t="s">
+      <c r="M8" s="32"/>
+      <c r="N8" s="73" t="s">
         <v>10</v>
       </c>
       <c r="O8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P8" s="19">
         <v>56</v>
@@ -2911,13 +2903,13 @@
       <c r="Q8" s="19">
         <v>64</v>
       </c>
-      <c r="R8" s="79">
+      <c r="R8" s="77">
         <v>72</v>
       </c>
-      <c r="S8" s="78">
+      <c r="S8" s="76">
         <v>80</v>
       </c>
-      <c r="T8" s="78">
+      <c r="T8" s="76">
         <f t="shared" si="2"/>
         <v>160</v>
       </c>
@@ -3055,18 +3047,18 @@
         <v>1</v>
       </c>
       <c r="J9" s="23"/>
-      <c r="K9" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="39"/>
-      <c r="M9" s="34">
+      <c r="K9" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="37"/>
+      <c r="M9" s="32">
         <v>5</v>
       </c>
-      <c r="N9" s="75" t="s">
+      <c r="N9" s="73" t="s">
         <v>11</v>
       </c>
       <c r="O9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P9" s="19">
         <v>63</v>
@@ -3074,13 +3066,13 @@
       <c r="Q9" s="19">
         <v>72</v>
       </c>
-      <c r="R9" s="78">
+      <c r="R9" s="76">
         <v>81</v>
       </c>
-      <c r="S9" s="78">
+      <c r="S9" s="76">
         <v>90</v>
       </c>
-      <c r="T9" s="78">
+      <c r="T9" s="76">
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
@@ -3218,18 +3210,18 @@
         <v>1</v>
       </c>
       <c r="J10" s="23"/>
-      <c r="K10" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" s="34">
+      <c r="K10" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="32">
         <v>4</v>
       </c>
-      <c r="M10" s="34"/>
-      <c r="N10" s="75" t="s">
+      <c r="M10" s="32"/>
+      <c r="N10" s="73" t="s">
         <v>12</v>
       </c>
       <c r="O10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P10" s="19">
         <v>70</v>
@@ -3241,17 +3233,17 @@
         <v>90</v>
       </c>
       <c r="S10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T10">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="U10" s="47">
+      <c r="U10" s="45">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
-      <c r="V10" s="47">
+      <c r="V10" s="45">
         <f t="shared" si="0"/>
         <v>220</v>
       </c>
@@ -3383,16 +3375,16 @@
       <c r="J11" s="16">
         <v>3</v>
       </c>
-      <c r="K11" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11" s="45"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="76" t="s">
+      <c r="K11" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="43"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="74" t="s">
         <v>13</v>
       </c>
       <c r="O11" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P11" s="16">
         <v>5</v>
@@ -3401,18 +3393,18 @@
         <v>5</v>
       </c>
       <c r="R11" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="S11" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="S11" s="44" t="s">
+        <v>27</v>
       </c>
       <c r="T11" s="16">
         <v>5</v>
       </c>
-      <c r="U11" s="48">
+      <c r="U11" s="46">
         <v>5</v>
       </c>
-      <c r="V11" s="48">
+      <c r="V11" s="46">
         <v>5</v>
       </c>
       <c r="W11" s="16">
@@ -3438,13 +3430,13 @@
         <f t="shared" si="1"/>
         <v>308</v>
       </c>
-      <c r="AC11" s="110" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD11" s="110"/>
-      <c r="AE11" s="110"/>
-      <c r="AF11" s="110"/>
-      <c r="AG11" s="110"/>
+      <c r="AC11" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD11" s="96"/>
+      <c r="AE11" s="96"/>
+      <c r="AF11" s="96"/>
+      <c r="AG11" s="96"/>
       <c r="AH11">
         <f t="shared" si="1"/>
         <v>374</v>
@@ -3525,13 +3517,13 @@
         <v>1</v>
       </c>
       <c r="J12" s="23"/>
-      <c r="K12" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="77" t="s">
-        <v>23</v>
+      <c r="K12" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="75" t="s">
+        <v>22</v>
       </c>
       <c r="O12">
         <v>72</v>
@@ -3552,11 +3544,11 @@
         <f t="shared" si="2"/>
         <v>240</v>
       </c>
-      <c r="U12" s="49">
+      <c r="U12" s="47">
         <f t="shared" si="0"/>
         <v>252</v>
       </c>
-      <c r="V12" s="49">
+      <c r="V12" s="47">
         <f t="shared" si="0"/>
         <v>264</v>
       </c>
@@ -3584,11 +3576,11 @@
         <f t="shared" si="1"/>
         <v>336</v>
       </c>
-      <c r="AC12" s="110"/>
-      <c r="AD12" s="110"/>
-      <c r="AE12" s="110"/>
-      <c r="AF12" s="110"/>
-      <c r="AG12" s="110"/>
+      <c r="AC12" s="96"/>
+      <c r="AD12" s="96"/>
+      <c r="AE12" s="96"/>
+      <c r="AF12" s="96"/>
+      <c r="AG12" s="96"/>
       <c r="AH12">
         <f t="shared" si="1"/>
         <v>408</v>
@@ -3733,11 +3725,11 @@
         <f t="shared" si="1"/>
         <v>364</v>
       </c>
-      <c r="AC13" s="110"/>
-      <c r="AD13" s="110"/>
-      <c r="AE13" s="110"/>
-      <c r="AF13" s="110"/>
-      <c r="AG13" s="110"/>
+      <c r="AC13" s="96"/>
+      <c r="AD13" s="96"/>
+      <c r="AE13" s="96"/>
+      <c r="AF13" s="96"/>
+      <c r="AG13" s="96"/>
       <c r="AH13">
         <f t="shared" si="1"/>
         <v>442</v>
@@ -3819,18 +3811,13 @@
       <c r="I14" s="20">
         <v>1</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="112">
         <v>28</v>
       </c>
-      <c r="K14">
-        <v>42</v>
-      </c>
-      <c r="L14">
-        <v>56</v>
-      </c>
-      <c r="N14">
-        <v>70</v>
-      </c>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
       <c r="O14">
         <v>84</v>
       </c>
@@ -3862,7 +3849,7 @@
         <f t="shared" si="0"/>
         <v>322</v>
       </c>
-      <c r="X14" s="32">
+      <c r="X14" s="30">
         <f t="shared" si="0"/>
         <v>336</v>
       </c>
@@ -3882,11 +3869,11 @@
         <f t="shared" si="2"/>
         <v>392</v>
       </c>
-      <c r="AC14" s="110"/>
-      <c r="AD14" s="110"/>
-      <c r="AE14" s="110"/>
-      <c r="AF14" s="110"/>
-      <c r="AG14" s="110"/>
+      <c r="AC14" s="96"/>
+      <c r="AD14" s="96"/>
+      <c r="AE14" s="96"/>
+      <c r="AF14" s="96"/>
+      <c r="AG14" s="96"/>
       <c r="AH14">
         <f t="shared" si="2"/>
         <v>476</v>
@@ -3971,10 +3958,10 @@
       <c r="J15">
         <v>30</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="97">
         <v>45</v>
       </c>
-      <c r="L15" s="26">
+      <c r="L15" s="98">
         <v>60</v>
       </c>
       <c r="M15" s="19"/>
@@ -4133,25 +4120,25 @@
       <c r="I16" s="20">
         <v>1</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="102">
         <v>32</v>
       </c>
-      <c r="K16" s="80" t="s">
+      <c r="K16" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="82"/>
+      <c r="L16" s="100"/>
+      <c r="M16" s="100"/>
+      <c r="N16" s="100"/>
+      <c r="O16" s="100"/>
+      <c r="P16" s="100"/>
+      <c r="Q16" s="100"/>
+      <c r="R16" s="100"/>
+      <c r="S16" s="100"/>
+      <c r="T16" s="100"/>
+      <c r="U16" s="100"/>
+      <c r="V16" s="100"/>
+      <c r="W16" s="100"/>
+      <c r="X16" s="101"/>
       <c r="Y16">
         <f t="shared" si="2"/>
         <v>400</v>
@@ -4269,13 +4256,13 @@
       <c r="I17" s="20">
         <v>1</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="102">
         <v>34</v>
       </c>
-      <c r="K17" s="27">
+      <c r="K17" s="25">
         <v>51</v>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="26">
         <v>68</v>
       </c>
       <c r="N17">
@@ -4360,7 +4347,7 @@
         <f t="shared" si="2"/>
         <v>595</v>
       </c>
-      <c r="AJ17" s="100">
+      <c r="AJ17" s="86">
         <f t="shared" si="4"/>
         <v>612</v>
       </c>
@@ -4433,13 +4420,13 @@
       <c r="I18" s="20">
         <v>1</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="102">
         <v>36</v>
       </c>
-      <c r="K18" s="29">
+      <c r="K18" s="27">
         <v>54</v>
       </c>
-      <c r="L18" s="30">
+      <c r="L18" s="28">
         <v>72</v>
       </c>
       <c r="N18">
@@ -4523,7 +4510,7 @@
         <f t="shared" si="2"/>
         <v>630</v>
       </c>
-      <c r="AJ18" s="100"/>
+      <c r="AJ18" s="86"/>
       <c r="AK18">
         <f t="shared" si="4"/>
         <v>666</v>
@@ -4578,13 +4565,13 @@
       <c r="D19" s="20">
         <v>1</v>
       </c>
-      <c r="E19" s="56">
-        <v>1</v>
-      </c>
-      <c r="F19" s="56">
-        <v>1</v>
-      </c>
-      <c r="G19" s="56">
+      <c r="E19" s="54">
+        <v>1</v>
+      </c>
+      <c r="F19" s="54">
+        <v>1</v>
+      </c>
+      <c r="G19" s="54">
         <v>1</v>
       </c>
       <c r="H19" s="20">
@@ -4647,27 +4634,27 @@
         <f t="shared" si="2"/>
         <v>494</v>
       </c>
-      <c r="AA19" s="61">
+      <c r="AA19" s="59">
         <f t="shared" si="2"/>
         <v>513</v>
       </c>
-      <c r="AB19" s="61">
+      <c r="AB19" s="59">
         <f t="shared" si="2"/>
         <v>532</v>
       </c>
-      <c r="AC19" s="61">
+      <c r="AC19" s="59">
         <f t="shared" si="2"/>
         <v>551</v>
       </c>
-      <c r="AD19" s="61">
+      <c r="AD19" s="59">
         <f t="shared" si="2"/>
         <v>570</v>
       </c>
-      <c r="AE19" s="61">
+      <c r="AE19" s="59">
         <f t="shared" si="2"/>
         <v>589</v>
       </c>
-      <c r="AF19" s="61">
+      <c r="AF19" s="59">
         <f t="shared" si="2"/>
         <v>608</v>
       </c>
@@ -4683,7 +4670,7 @@
         <f t="shared" si="2"/>
         <v>665</v>
       </c>
-      <c r="AJ19" s="100"/>
+      <c r="AJ19" s="86"/>
       <c r="AK19">
         <f t="shared" si="4"/>
         <v>703</v>
@@ -4738,13 +4725,13 @@
       <c r="D20" s="20">
         <v>1</v>
       </c>
-      <c r="E20" s="57">
-        <v>1</v>
-      </c>
-      <c r="F20" s="57">
-        <v>1</v>
-      </c>
-      <c r="G20" s="57">
+      <c r="E20" s="55">
+        <v>1</v>
+      </c>
+      <c r="F20" s="55">
+        <v>1</v>
+      </c>
+      <c r="G20" s="55">
         <v>1</v>
       </c>
       <c r="H20" s="20">
@@ -4805,29 +4792,29 @@
         <v>500</v>
       </c>
       <c r="Z20" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA20" s="61">
+        <v>31</v>
+      </c>
+      <c r="AA20" s="59">
         <f t="shared" si="2"/>
         <v>540</v>
       </c>
-      <c r="AB20" s="61">
+      <c r="AB20" s="59">
         <f t="shared" si="2"/>
         <v>560</v>
       </c>
-      <c r="AC20" s="62">
+      <c r="AC20" s="60">
         <f t="shared" si="2"/>
         <v>580</v>
       </c>
-      <c r="AD20" s="63">
+      <c r="AD20" s="61">
         <f t="shared" si="2"/>
         <v>600</v>
       </c>
-      <c r="AE20" s="64">
+      <c r="AE20" s="62">
         <f t="shared" si="2"/>
         <v>620</v>
       </c>
-      <c r="AF20" s="61">
+      <c r="AF20" s="59">
         <f t="shared" si="2"/>
         <v>640</v>
       </c>
@@ -4843,7 +4830,7 @@
         <f t="shared" si="2"/>
         <v>700</v>
       </c>
-      <c r="AJ20" s="100"/>
+      <c r="AJ20" s="86"/>
       <c r="AK20">
         <f t="shared" si="4"/>
         <v>740</v>
@@ -4898,16 +4885,16 @@
       <c r="D21" s="20">
         <v>1</v>
       </c>
-      <c r="E21" s="58">
-        <v>1</v>
-      </c>
-      <c r="F21" s="58">
-        <v>1</v>
-      </c>
-      <c r="G21" s="58">
-        <v>1</v>
-      </c>
-      <c r="H21" s="60">
+      <c r="E21" s="56">
+        <v>1</v>
+      </c>
+      <c r="F21" s="56">
+        <v>1</v>
+      </c>
+      <c r="G21" s="56">
+        <v>1</v>
+      </c>
+      <c r="H21" s="58">
         <v>1</v>
       </c>
       <c r="I21" s="20">
@@ -4937,10 +4924,10 @@
       <c r="R21">
         <v>189</v>
       </c>
-      <c r="S21" s="54">
+      <c r="S21" s="52">
         <v>210</v>
       </c>
-      <c r="T21" s="55">
+      <c r="T21" s="53">
         <f t="shared" si="2"/>
         <v>420</v>
       </c>
@@ -4948,7 +4935,7 @@
         <f t="shared" si="2"/>
         <v>441</v>
       </c>
-      <c r="V21" s="47">
+      <c r="V21" s="45">
         <f t="shared" si="2"/>
         <v>462</v>
       </c>
@@ -4956,7 +4943,7 @@
         <f t="shared" si="2"/>
         <v>483</v>
       </c>
-      <c r="X21" s="47">
+      <c r="X21" s="45">
         <f t="shared" si="2"/>
         <v>504</v>
       </c>
@@ -4968,27 +4955,27 @@
         <f t="shared" si="2"/>
         <v>546</v>
       </c>
-      <c r="AA21" s="61">
+      <c r="AA21" s="59">
         <f t="shared" si="2"/>
         <v>567</v>
       </c>
-      <c r="AB21" s="61">
+      <c r="AB21" s="59">
         <f t="shared" si="2"/>
         <v>588</v>
       </c>
-      <c r="AC21" s="65">
+      <c r="AC21" s="63">
         <f t="shared" si="2"/>
         <v>609</v>
       </c>
-      <c r="AD21" s="72">
+      <c r="AD21" s="70">
         <f t="shared" si="2"/>
         <v>630</v>
       </c>
-      <c r="AE21" s="66">
+      <c r="AE21" s="64">
         <f t="shared" si="2"/>
         <v>651</v>
       </c>
-      <c r="AF21" s="61">
+      <c r="AF21" s="59">
         <f t="shared" si="2"/>
         <v>672</v>
       </c>
@@ -5004,7 +4991,7 @@
         <f t="shared" si="2"/>
         <v>735</v>
       </c>
-      <c r="AJ21" s="100"/>
+      <c r="AJ21" s="86"/>
       <c r="AK21">
         <f t="shared" si="4"/>
         <v>777</v>
@@ -5059,13 +5046,13 @@
       <c r="D22" s="20">
         <v>1</v>
       </c>
-      <c r="E22" s="59">
-        <v>1</v>
-      </c>
-      <c r="F22" s="59">
-        <v>1</v>
-      </c>
-      <c r="G22" s="59">
+      <c r="E22" s="57">
+        <v>1</v>
+      </c>
+      <c r="F22" s="57">
+        <v>1</v>
+      </c>
+      <c r="G22" s="57">
         <v>1</v>
       </c>
       <c r="H22" s="20">
@@ -5077,12 +5064,12 @@
       <c r="J22">
         <v>44</v>
       </c>
-      <c r="K22" s="83" t="s">
+      <c r="K22" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="L22" s="84"/>
-      <c r="M22" s="84"/>
-      <c r="N22" s="85"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="104"/>
+      <c r="N22" s="105"/>
       <c r="O22">
         <v>132</v>
       </c>
@@ -5095,14 +5082,14 @@
       <c r="R22">
         <v>198</v>
       </c>
-      <c r="S22" s="92" t="s">
-        <v>1</v>
-      </c>
-      <c r="T22" s="93"/>
-      <c r="U22" s="94"/>
-      <c r="V22" s="93"/>
-      <c r="W22" s="94"/>
-      <c r="X22" s="95"/>
+      <c r="S22" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="79"/>
+      <c r="U22" s="80"/>
+      <c r="V22" s="79"/>
+      <c r="W22" s="80"/>
+      <c r="X22" s="81"/>
       <c r="Y22">
         <f t="shared" si="2"/>
         <v>550</v>
@@ -5111,27 +5098,27 @@
         <f t="shared" si="2"/>
         <v>572</v>
       </c>
-      <c r="AA22" s="61">
+      <c r="AA22" s="59">
         <f t="shared" si="2"/>
         <v>594</v>
       </c>
-      <c r="AB22" s="61">
+      <c r="AB22" s="59">
         <f t="shared" si="2"/>
         <v>616</v>
       </c>
-      <c r="AC22" s="65">
+      <c r="AC22" s="63">
         <f t="shared" si="2"/>
         <v>638</v>
       </c>
-      <c r="AD22" s="70">
+      <c r="AD22" s="68">
         <f t="shared" si="2"/>
         <v>660</v>
       </c>
-      <c r="AE22" s="66">
+      <c r="AE22" s="64">
         <f t="shared" si="2"/>
         <v>682</v>
       </c>
-      <c r="AF22" s="61">
+      <c r="AF22" s="59">
         <f t="shared" si="2"/>
         <v>704</v>
       </c>
@@ -5147,7 +5134,7 @@
         <f t="shared" si="2"/>
         <v>770</v>
       </c>
-      <c r="AJ22" s="100"/>
+      <c r="AJ22" s="86"/>
       <c r="AK22">
         <f t="shared" si="4"/>
         <v>814</v>
@@ -5222,10 +5209,10 @@
         <f t="shared" si="6"/>
         <v>230</v>
       </c>
-      <c r="K23" s="86"/>
-      <c r="L23" s="87"/>
-      <c r="M23" s="87"/>
-      <c r="N23" s="88"/>
+      <c r="K23" s="106"/>
+      <c r="L23" s="107"/>
+      <c r="M23" s="107"/>
+      <c r="N23" s="108"/>
       <c r="O23">
         <f t="shared" si="6"/>
         <v>345</v>
@@ -5242,12 +5229,12 @@
         <f t="shared" si="6"/>
         <v>414</v>
       </c>
-      <c r="S23" s="96"/>
-      <c r="T23" s="93"/>
-      <c r="U23" s="93"/>
-      <c r="V23" s="93"/>
-      <c r="W23" s="93"/>
-      <c r="X23" s="95"/>
+      <c r="S23" s="82"/>
+      <c r="T23" s="79"/>
+      <c r="U23" s="79"/>
+      <c r="V23" s="79"/>
+      <c r="W23" s="79"/>
+      <c r="X23" s="81"/>
       <c r="Y23">
         <f t="shared" si="2"/>
         <v>575</v>
@@ -5256,27 +5243,27 @@
         <f t="shared" si="2"/>
         <v>598</v>
       </c>
-      <c r="AA23" s="61">
+      <c r="AA23" s="59">
         <f t="shared" si="2"/>
         <v>621</v>
       </c>
-      <c r="AB23" s="61">
+      <c r="AB23" s="59">
         <f t="shared" si="2"/>
         <v>644</v>
       </c>
-      <c r="AC23" s="65">
+      <c r="AC23" s="63">
         <f t="shared" si="2"/>
         <v>667</v>
       </c>
-      <c r="AD23" s="71">
+      <c r="AD23" s="69">
         <f t="shared" si="2"/>
         <v>690</v>
       </c>
-      <c r="AE23" s="66">
+      <c r="AE23" s="64">
         <f t="shared" si="2"/>
         <v>713</v>
       </c>
-      <c r="AF23" s="61">
+      <c r="AF23" s="59">
         <f t="shared" si="2"/>
         <v>736</v>
       </c>
@@ -5292,7 +5279,7 @@
         <f t="shared" si="2"/>
         <v>805</v>
       </c>
-      <c r="AJ23" s="100"/>
+      <c r="AJ23" s="86"/>
       <c r="AK23">
         <f t="shared" si="4"/>
         <v>851</v>
@@ -5367,10 +5354,10 @@
         <f t="shared" si="6"/>
         <v>240</v>
       </c>
-      <c r="K24" s="89"/>
-      <c r="L24" s="90"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="91"/>
+      <c r="K24" s="109"/>
+      <c r="L24" s="110"/>
+      <c r="M24" s="110"/>
+      <c r="N24" s="111"/>
       <c r="O24">
         <f t="shared" si="6"/>
         <v>360</v>
@@ -5387,12 +5374,12 @@
         <f t="shared" si="6"/>
         <v>432</v>
       </c>
-      <c r="S24" s="97"/>
-      <c r="T24" s="93"/>
-      <c r="U24" s="98"/>
-      <c r="V24" s="93"/>
-      <c r="W24" s="98"/>
-      <c r="X24" s="99"/>
+      <c r="S24" s="83"/>
+      <c r="T24" s="79"/>
+      <c r="U24" s="84"/>
+      <c r="V24" s="79"/>
+      <c r="W24" s="84"/>
+      <c r="X24" s="85"/>
       <c r="Y24">
         <f t="shared" si="2"/>
         <v>600</v>
@@ -5401,27 +5388,27 @@
         <f t="shared" si="2"/>
         <v>624</v>
       </c>
-      <c r="AA24" s="61">
+      <c r="AA24" s="59">
         <f t="shared" si="2"/>
         <v>648</v>
       </c>
-      <c r="AB24" s="61">
+      <c r="AB24" s="59">
         <f t="shared" si="2"/>
         <v>672</v>
       </c>
-      <c r="AC24" s="65">
+      <c r="AC24" s="63">
         <f t="shared" si="2"/>
         <v>696</v>
       </c>
-      <c r="AD24" s="71">
+      <c r="AD24" s="69">
         <f t="shared" si="2"/>
         <v>720</v>
       </c>
-      <c r="AE24" s="66">
+      <c r="AE24" s="64">
         <f t="shared" si="2"/>
         <v>744</v>
       </c>
-      <c r="AF24" s="61">
+      <c r="AF24" s="59">
         <f t="shared" si="2"/>
         <v>768</v>
       </c>
@@ -5437,7 +5424,7 @@
         <f t="shared" si="2"/>
         <v>840</v>
       </c>
-      <c r="AJ24" s="100"/>
+      <c r="AJ24" s="86"/>
       <c r="AK24">
         <f t="shared" si="4"/>
         <v>888</v>
@@ -5544,7 +5531,7 @@
         <f t="shared" si="6"/>
         <v>475</v>
       </c>
-      <c r="T25" s="52">
+      <c r="T25" s="50">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
@@ -5552,7 +5539,7 @@
         <f t="shared" si="2"/>
         <v>525</v>
       </c>
-      <c r="V25" s="52">
+      <c r="V25" s="50">
         <f t="shared" si="2"/>
         <v>550</v>
       </c>
@@ -5572,27 +5559,27 @@
         <f t="shared" si="2"/>
         <v>650</v>
       </c>
-      <c r="AA25" s="61">
+      <c r="AA25" s="59">
         <f t="shared" si="2"/>
         <v>675</v>
       </c>
-      <c r="AB25" s="61">
+      <c r="AB25" s="59">
         <f t="shared" si="2"/>
         <v>700</v>
       </c>
-      <c r="AC25" s="65">
+      <c r="AC25" s="63">
         <f t="shared" si="2"/>
         <v>725</v>
       </c>
-      <c r="AD25" s="71">
+      <c r="AD25" s="69">
         <f t="shared" si="2"/>
         <v>750</v>
       </c>
-      <c r="AE25" s="66">
+      <c r="AE25" s="64">
         <f t="shared" si="2"/>
         <v>775</v>
       </c>
-      <c r="AF25" s="61">
+      <c r="AF25" s="59">
         <f t="shared" si="2"/>
         <v>800</v>
       </c>
@@ -5608,7 +5595,7 @@
         <f t="shared" si="2"/>
         <v>875</v>
       </c>
-      <c r="AJ25" s="100"/>
+      <c r="AJ25" s="86"/>
       <c r="AK25">
         <f t="shared" si="4"/>
         <v>925</v>
@@ -5743,27 +5730,27 @@
         <f t="shared" si="2"/>
         <v>676</v>
       </c>
-      <c r="AA26" s="61">
+      <c r="AA26" s="59">
         <f t="shared" si="2"/>
         <v>702</v>
       </c>
-      <c r="AB26" s="61">
+      <c r="AB26" s="59">
         <f t="shared" si="2"/>
         <v>728</v>
       </c>
-      <c r="AC26" s="65">
+      <c r="AC26" s="63">
         <f t="shared" si="2"/>
         <v>754</v>
       </c>
-      <c r="AD26" s="70">
+      <c r="AD26" s="68">
         <f t="shared" si="2"/>
         <v>780</v>
       </c>
-      <c r="AE26" s="66">
+      <c r="AE26" s="64">
         <f t="shared" si="2"/>
         <v>806</v>
       </c>
-      <c r="AF26" s="61">
+      <c r="AF26" s="59">
         <f t="shared" si="2"/>
         <v>832</v>
       </c>
@@ -5779,7 +5766,7 @@
         <f t="shared" si="2"/>
         <v>910</v>
       </c>
-      <c r="AJ26" s="100"/>
+      <c r="AJ26" s="86"/>
       <c r="AK26">
         <f t="shared" si="4"/>
         <v>962</v>
@@ -5862,23 +5849,23 @@
         <f t="shared" si="6"/>
         <v>324</v>
       </c>
-      <c r="N27" s="53">
+      <c r="N27" s="51">
         <f t="shared" si="6"/>
         <v>378</v>
       </c>
-      <c r="O27" s="53">
+      <c r="O27" s="51">
         <f t="shared" si="6"/>
         <v>405</v>
       </c>
-      <c r="P27" s="53">
+      <c r="P27" s="51">
         <f t="shared" si="6"/>
         <v>432</v>
       </c>
-      <c r="Q27" s="53">
+      <c r="Q27" s="51">
         <f t="shared" si="6"/>
         <v>459</v>
       </c>
-      <c r="R27" s="53">
+      <c r="R27" s="51">
         <f t="shared" si="6"/>
         <v>486</v>
       </c>
@@ -5914,27 +5901,27 @@
         <f t="shared" si="2"/>
         <v>702</v>
       </c>
-      <c r="AA27" s="61">
+      <c r="AA27" s="59">
         <f t="shared" si="2"/>
         <v>729</v>
       </c>
-      <c r="AB27" s="61">
+      <c r="AB27" s="59">
         <f t="shared" si="2"/>
         <v>756</v>
       </c>
-      <c r="AC27" s="65">
+      <c r="AC27" s="63">
         <f t="shared" si="2"/>
         <v>783</v>
       </c>
-      <c r="AD27" s="73">
+      <c r="AD27" s="71">
         <f t="shared" si="2"/>
         <v>810</v>
       </c>
-      <c r="AE27" s="66">
+      <c r="AE27" s="64">
         <f t="shared" si="2"/>
         <v>837</v>
       </c>
-      <c r="AF27" s="61">
+      <c r="AF27" s="59">
         <f t="shared" si="2"/>
         <v>864</v>
       </c>
@@ -5950,7 +5937,7 @@
         <f t="shared" si="2"/>
         <v>945</v>
       </c>
-      <c r="AJ27" s="100"/>
+      <c r="AJ27" s="86"/>
       <c r="AK27">
         <f t="shared" si="4"/>
         <v>999</v>
@@ -6033,23 +6020,23 @@
         <f t="shared" si="6"/>
         <v>336</v>
       </c>
-      <c r="N28" s="53">
+      <c r="N28" s="51">
         <f t="shared" si="6"/>
         <v>392</v>
       </c>
-      <c r="O28" s="53">
+      <c r="O28" s="51">
         <f t="shared" si="6"/>
         <v>420</v>
       </c>
-      <c r="P28" s="53">
+      <c r="P28" s="51">
         <f t="shared" si="6"/>
         <v>448</v>
       </c>
-      <c r="Q28" s="53">
+      <c r="Q28" s="51">
         <f t="shared" si="6"/>
         <v>476</v>
       </c>
-      <c r="R28" s="53">
+      <c r="R28" s="51">
         <f t="shared" si="6"/>
         <v>504</v>
       </c>
@@ -6085,27 +6072,27 @@
         <f t="shared" si="2"/>
         <v>728</v>
       </c>
-      <c r="AA28" s="61">
+      <c r="AA28" s="59">
         <f t="shared" si="2"/>
         <v>756</v>
       </c>
-      <c r="AB28" s="61">
+      <c r="AB28" s="59">
         <f t="shared" si="2"/>
         <v>784</v>
       </c>
-      <c r="AC28" s="67">
+      <c r="AC28" s="65">
         <f t="shared" si="2"/>
         <v>812</v>
       </c>
-      <c r="AD28" s="68">
+      <c r="AD28" s="66">
         <f t="shared" si="2"/>
         <v>840</v>
       </c>
-      <c r="AE28" s="69">
+      <c r="AE28" s="67">
         <f t="shared" si="2"/>
         <v>868</v>
       </c>
-      <c r="AF28" s="61">
+      <c r="AF28" s="59">
         <f t="shared" si="2"/>
         <v>896</v>
       </c>
@@ -6121,7 +6108,7 @@
         <f t="shared" si="2"/>
         <v>980</v>
       </c>
-      <c r="AJ28" s="100"/>
+      <c r="AJ28" s="86"/>
       <c r="AK28">
         <f t="shared" si="4"/>
         <v>1036</v>
@@ -6204,23 +6191,23 @@
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N29" s="53">
+      <c r="N29" s="51">
         <f t="shared" si="6"/>
         <v>406</v>
       </c>
-      <c r="O29" s="53">
+      <c r="O29" s="51">
         <f t="shared" si="6"/>
         <v>435</v>
       </c>
-      <c r="P29" s="53">
+      <c r="P29" s="51">
         <f t="shared" si="6"/>
         <v>464</v>
       </c>
-      <c r="Q29" s="53">
+      <c r="Q29" s="51">
         <f t="shared" si="6"/>
         <v>493</v>
       </c>
-      <c r="R29" s="53">
+      <c r="R29" s="51">
         <f t="shared" si="6"/>
         <v>522</v>
       </c>
@@ -6253,27 +6240,27 @@
         <f t="shared" si="2"/>
         <v>754</v>
       </c>
-      <c r="AA29" s="61">
+      <c r="AA29" s="59">
         <f t="shared" si="2"/>
         <v>783</v>
       </c>
-      <c r="AB29" s="61">
+      <c r="AB29" s="59">
         <f t="shared" si="2"/>
         <v>812</v>
       </c>
-      <c r="AC29" s="61">
+      <c r="AC29" s="59">
         <f t="shared" si="2"/>
         <v>841</v>
       </c>
-      <c r="AD29" s="61">
+      <c r="AD29" s="59">
         <f t="shared" si="2"/>
         <v>870</v>
       </c>
-      <c r="AE29" s="61">
+      <c r="AE29" s="59">
         <f t="shared" si="2"/>
         <v>899</v>
       </c>
-      <c r="AF29" s="61">
+      <c r="AF29" s="59">
         <f t="shared" si="2"/>
         <v>928</v>
       </c>
@@ -6403,7 +6390,7 @@
         <f t="shared" si="2"/>
         <v>600</v>
       </c>
-      <c r="U30" s="33">
+      <c r="U30" s="31">
         <f t="shared" si="2"/>
         <v>630</v>
       </c>
@@ -6683,13 +6670,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="K16:X16"/>
     <mergeCell ref="K22:N24"/>
     <mergeCell ref="S22:X24"/>
     <mergeCell ref="AJ17:AJ28"/>
     <mergeCell ref="V4:X7"/>
     <mergeCell ref="AC11:AG14"/>
+    <mergeCell ref="J14:N14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
